--- a/storage/Excel/generusTemplate_daerah.xlsx
+++ b/storage/Excel/generusTemplate_daerah.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="12430" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12000"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Nama</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t>MANDUNGAN SELATAN - DESA TIMUR</t>
+  </si>
+  <si>
+    <t>MANDUNGAN SELATAN 2 - DESA TIMUR</t>
   </si>
   <si>
     <t>MANDUNGAN UTARA - DESA TIMUR</t>
@@ -1250,19 +1253,19 @@
       <formula1>"L,P"</formula1>
     </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="Pick from list" prompt="Please pick a value from the drop-down list." sqref="D2:D150" errorStyle="information">
-      <formula1>"Sambi,Mangu,Desa Timur,Desa Barat,Desa Tengah"</formula1>
+      <formula1>"Desa Timur"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E99 E100:E150">
-      <formula1>Sheet1!$A$1:$A$45</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E158">
+      <formula1>Sheet1!$A$1:$A$96</formula1>
     </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="Pick from list" prompt="Please pick a value from the drop-down list." sqref="F2:F150" errorStyle="information">
       <formula1>"Balita,Caberawit,Pra Remaja,Remaja,Usia Mandiri"</formula1>
     </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="Pick from list" prompt="Please pick a value from the drop-down list." sqref="G2:G150" errorStyle="information">
-      <formula1>"SD,SMP,SMA,D3,S1,S2,S3"</formula1>
+      <formula1>"BELUM SEKOLAH,TK,SD,SMP,SMA,D3,S1,S2,S3"</formula1>
     </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="Pick from list" prompt="Please pick a value from the drop-down list." sqref="H2:H150" errorStyle="information">
-      <formula1>"PELAJAR/MAHASISWA,BEKERJA,BELUM BEKERJA,MONDOK"</formula1>
+      <formula1>"BELUM SEKOLAH,PELAJAR/MAHASISWA,BEKERJA,BELUM BEKERJA,MONDOK"</formula1>
     </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="Pick from list" prompt="Please pick a value from the drop-down list." sqref="K2:K150 M2:M150" errorStyle="information">
       <formula1>"Tidak,Ya"</formula1>
@@ -1280,7 +1283,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -1511,6 +1514,11 @@
         <v>59</v>
       </c>
     </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/storage/Excel/generusTemplate_daerah.xlsx
+++ b/storage/Excel/generusTemplate_daerah.xlsx
@@ -1252,8 +1252,8 @@
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="Pick from list" prompt="Please pick a value from the drop-down list." sqref="C2:C150" errorStyle="information">
       <formula1>"L,P"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="Pick from list" prompt="Please pick a value from the drop-down list." sqref="D2:D150" errorStyle="information">
-      <formula1>"Desa Timur"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D150">
+      <formula1>"Sambi,Mangu,Desa Timur,Desa Barat,Desa Tengah"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E158">
       <formula1>Sheet1!$A$1:$A$96</formula1>

--- a/storage/Excel/generusTemplate_daerah.xlsx
+++ b/storage/Excel/generusTemplate_daerah.xlsx
@@ -1248,7 +1248,10 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="8">
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
+      <formula1>"BELUM SEKOLAH,PELAJAR,MAHASISWA,BEKERJA,BELUM BEKERJA,MONDOK"</formula1>
+    </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="Pick from list" prompt="Please pick a value from the drop-down list." sqref="C2:C150" errorStyle="information">
       <formula1>"L,P"</formula1>
     </dataValidation>
@@ -1264,7 +1267,7 @@
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="Pick from list" prompt="Please pick a value from the drop-down list." sqref="G2:G150" errorStyle="information">
       <formula1>"BELUM SEKOLAH,TK,SD,SMP,SMA,D3,S1,S2,S3"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="Pick from list" prompt="Please pick a value from the drop-down list." sqref="H2:H150" errorStyle="information">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="Pick from list" prompt="Please pick a value from the drop-down list." sqref="H3:H150" errorStyle="information">
       <formula1>"BELUM SEKOLAH,PELAJAR/MAHASISWA,BEKERJA,BELUM BEKERJA,MONDOK"</formula1>
     </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="Pick from list" prompt="Please pick a value from the drop-down list." sqref="K2:K150 M2:M150" errorStyle="information">
